--- a/example_run/rfqs_sent.xlsx
+++ b/example_run/rfqs_sent.xlsx
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -725,7 +725,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>No saved email contact or portal login for 'ElectroConn' - this source hasn't been explored yet. Needs manual outreach before qualification or an RFQ can proceed.</t>
+          <t>'ElectroConn' is not yet an approved vendor (ISO 9001 status: Unknown) - needs qualification review before an RFQ can be sent.</t>
         </is>
       </c>
     </row>
@@ -735,7 +735,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>No saved email contact or portal login for 'MeanTech' - this source hasn't been explored yet. Needs manual outreach before qualification or an RFQ can proceed.</t>
+          <t>'MeanTech' is not yet an approved vendor (ISO 9001 status: Unknown) - needs qualification review before an RFQ can be sent.</t>
         </is>
       </c>
     </row>
@@ -776,6 +776,26 @@
       <c r="B19" t="inlineStr">
         <is>
           <t>RFQ to 'AndyMark' drafted but not sent (no SMTP access).</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>7</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Distributor part - pricing should come from a Stage 2 catalog query, not an RFQ. Skipped here.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>9</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Distributor part - pricing should come from a Stage 2 catalog query, not an RFQ. Skipped here.</t>
         </is>
       </c>
     </row>
